--- a/results/Int All Data 0.5/Rando_7_permute.xlsx
+++ b/results/Int All Data 0.5/Rando_7_permute.xlsx
@@ -440,843 +440,843 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9745920419413902</v>
+        <v>0.9746233078870223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9726235380043823</v>
+        <v>0.9746233078870223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9706550340673744</v>
+        <v>0.9769094738316542</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9706550340673744</v>
+        <v>0.9769094738316542</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9800235620166284</v>
+        <v>0.9778937258001581</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9800235620166284</v>
+        <v>0.9778937258001581</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9800235620166284</v>
+        <v>0.9778937258001581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9735765240272539</v>
+        <v>0.9759252218631502</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9732588620196301</v>
+        <v>0.9756075598555263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9771958698936458</v>
+        <v>0.9756075598555263</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9804975537524138</v>
+        <v>0.9775760637925341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9804975537524138</v>
+        <v>0.9778937258001581</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9814818057209177</v>
+        <v>0.9749409698946463</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9844345616264295</v>
+        <v>0.9719882139891345</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9814818057209177</v>
+        <v>0.9729724659576384</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.976560545878398</v>
+        <v>0.9769094738316542</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9617967663508389</v>
+        <v>0.979862229737166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9621144283584628</v>
+        <v>0.9729724659576384</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9621144283584628</v>
+        <v>0.9729724659576384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9617967663508389</v>
+        <v>0.9719882139891345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.957510830523567</v>
+        <v>0.9739567179261424</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9536050885951836</v>
+        <v>0.9739567179261424</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9536050885951836</v>
+        <v>0.9739567179261424</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9568755065083192</v>
+        <v>0.9739567179261424</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9568755065083192</v>
+        <v>0.9739567179261424</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9519542466657995</v>
+        <v>0.9749409698946463</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9319515452880969</v>
+        <v>0.9749409698946463</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.91521926182353</v>
+        <v>0.9746233078870223</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9214424356421775</v>
+        <v>0.9726548039500145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9270302854455772</v>
+        <v>0.9716705519815105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9240775295400654</v>
+        <v>0.9726548039500145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9240775295400654</v>
+        <v>0.9578910244224554</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9112822539495142</v>
+        <v>0.9588752763909594</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9112822539495142</v>
+        <v>0.9431272448948964</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9112822539495142</v>
+        <v>0.9431272448948964</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9125841679256421</v>
+        <v>0.9391902370208807</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9086471600516264</v>
+        <v>0.9431272448948964</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9076629080831224</v>
+        <v>0.9431272448948964</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9175054277681618</v>
+        <v>0.9460800008004082</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9175054277681618</v>
+        <v>0.9529697645799358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9184896797366657</v>
+        <v>0.9411587409578885</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9319515452880969</v>
+        <v>0.9224579535563138</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8738806791463647</v>
+        <v>0.9224579535563138</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8719121752093568</v>
+        <v>0.919505197650802</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8331774204844471</v>
+        <v>0.8850563787531641</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8171117269807602</v>
+        <v>0.8998201582807231</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8187625689101442</v>
+        <v>0.8998201582807231</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8187625689101442</v>
+        <v>0.9067099220602508</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8187625689101442</v>
+        <v>0.9103292679266426</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8478524047264104</v>
+        <v>0.9103292679266426</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8498209086634183</v>
+        <v>0.8955654883990836</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8511228226395462</v>
+        <v>0.8955654883990836</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8612830043322095</v>
+        <v>0.9004867482416032</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8612830043322095</v>
+        <v>0.8965497403675875</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8793484677185364</v>
+        <v>0.8955654883990836</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8773799637815285</v>
+        <v>0.8955654883990836</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8662355301203615</v>
+        <v>0.9054080080841229</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8728388978378974</v>
+        <v>0.8676575053277171</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8715057179161372</v>
+        <v>0.8757553852464757</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8741408118140251</v>
+        <v>0.8757553852464757</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8738231498064013</v>
+        <v>0.8518156759947573</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8669646519725061</v>
+        <v>0.8455299702848452</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8689331559095139</v>
+        <v>0.8485139921359894</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8771248336651692</v>
+        <v>0.8475297401674855</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8748386677205375</v>
+        <v>0.8475297401674855</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8541068444906903</v>
+        <v>0.8563567419383886</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.781938788782279</v>
+        <v>0.8527373960719967</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8465817566959148</v>
+        <v>0.8527373960719967</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8515030165384345</v>
+        <v>0.846165294300093</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8627099820908664</v>
+        <v>0.8333700187095419</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8827439494142012</v>
+        <v>0.8372132287466608</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.9405284194939418</v>
+        <v>0.8053995037469109</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.9405284194939418</v>
+        <v>0.8053995037469109</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.9481160391799819</v>
+        <v>0.8095603757916537</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.9179844220552482</v>
+        <v>0.8007333740207505</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8918210787501626</v>
+        <v>0.7892400124063272</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8921387407577865</v>
+        <v>0.792192768311839</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8921387407577865</v>
+        <v>0.792859358272719</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8921387407577865</v>
+        <v>0.8030820718566469</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.9131256941039931</v>
+        <v>0.8117477413480876</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.9140786801268648</v>
+        <v>0.7897452700877448</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.9121727080811214</v>
+        <v>0.7558379773684578</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7817149246115519</v>
+        <v>0.7292319082732194</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7633630651632333</v>
+        <v>0.7626964752023533</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,701 +1286,701 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7164991645739327</v>
+        <v>0.7317732043342104</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6833209937067904</v>
+        <v>0.7435842279562577</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7002146094508199</v>
+        <v>0.7268206785460585</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6963401334680687</v>
+        <v>0.7258364265775545</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7327574563027144</v>
+        <v>0.7389493641757297</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7327574563027144</v>
+        <v>0.7389493641757297</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7389180982300974</v>
+        <v>0.7291068444906903</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7389180982300974</v>
+        <v>0.719613252758907</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7304087584668181</v>
+        <v>0.6989439614203243</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7323772624038259</v>
+        <v>0.6503979529560076</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7222170807111628</v>
+        <v>0.6789412600426217</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7202485767741549</v>
+        <v>0.6490960389798797</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7479326956747941</v>
+        <v>0.6490960389798797</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7617434891794815</v>
+        <v>0.6668438403585829</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7713621446937938</v>
+        <v>0.6825918718546459</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7775853185124413</v>
+        <v>0.667192768311839</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7766010665439373</v>
+        <v>0.664875336421575</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7766010665439373</v>
+        <v>0.6891639736265496</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7083074868182773</v>
+        <v>0.5666114718506439</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5453068564968134</v>
+        <v>0.5462598425196851</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5453068564968134</v>
+        <v>0.5554670381894766</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6046796366146735</v>
+        <v>0.5554670381894766</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.597789872835146</v>
+        <v>0.5515300303154609</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5987741248036499</v>
+        <v>0.5226377952755905</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6027736645689301</v>
+        <v>0.5246062992125984</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6076636584658176</v>
+        <v>0.5246062992125984</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6145534222453451</v>
+        <v>0.5420051726380454</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6145534222453451</v>
+        <v>0.5420051726380454</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6149023501986013</v>
+        <v>0.5420051726380454</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6165531921279852</v>
+        <v>0.5246062992125984</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6142357602377212</v>
+        <v>0.5252728891734785</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6132515082692173</v>
+        <v>0.5252728891734785</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6151887462605929</v>
+        <v>0.5352092066954147</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6415396852394721</v>
+        <v>0.5427655604358222</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6415396852394721</v>
+        <v>0.5203828952765911</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6431279952775916</v>
+        <v>0.5056191157490321</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6441435131917278</v>
+        <v>0.506603367717536</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6063617444896897</v>
+        <v>0.5085718716545439</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6409668931154889</v>
+        <v>0.5125088795285596</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6071846641787312</v>
+        <v>0.5125088795285596</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6071846641787312</v>
+        <v>0.5125088795285596</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6419198791383606</v>
+        <v>0.5345426167345346</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6613185224464477</v>
+        <v>0.5266686009865031</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6202350698856417</v>
+        <v>0.539432610631422</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5689914356321725</v>
+        <v>0.539432610631422</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5762613933105883</v>
+        <v>0.5433696185054377</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5762613933105883</v>
+        <v>0.5351779407497824</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6178188376071796</v>
+        <v>0.5361621927182864</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6181364996148035</v>
+        <v>0.5276215870093748</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6181364996148035</v>
+        <v>0.6103300183093378</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.610929073827652</v>
+        <v>0.6044245064983141</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.610929073827652</v>
+        <v>0.641857347247096</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.610929073827652</v>
+        <v>0.5587374561026123</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.6238494132007324</v>
+        <v>0.5383858267716536</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.6326764149716355</v>
+        <v>0.5403543307086615</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.6509607399773885</v>
+        <v>0.5088582677165354</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.6573715094698296</v>
+        <v>0.5108267716535433</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4993959419303845</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4984116899618806</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4984116899618806</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5016821078750163</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5016821078750163</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5019997698826402</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5019997698826402</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5019997698826402</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5019997698826402</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5019997698826402</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5003489279532561</v>
+        <v>0.4996823379923761</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003489279532561</v>
+        <v>0.4996823379923761</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5000312659456323</v>
+        <v>0.4996823379923761</v>
       </c>
     </row>
   </sheetData>
